--- a/tests/book/fixtures/charts-openpyxl.xlsx
+++ b/tests/book/fixtures/charts-openpyxl.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pie" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scatter" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,6 +574,17 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Sales'!$A$2:$A$7</f>
@@ -586,6 +598,209 @@
         </ser>
         <firstSliceAng val="0"/>
       </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Atari and PC</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <doughnutChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Sales'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sales'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sales'!$C$2:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Sales'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sales'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sales'!$D$2:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+        <holeSize val="60"/>
+      </doughnutChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Speed and price by MHz</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Scatter'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Scatter'!$A$2:$A$6</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Scatter'!$B$2:$B$6</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Scatter'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="diamond"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Scatter'!$A$2:$A$6</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Scatter'!$C$2:$C$6</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -672,6 +887,55 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1122,4 +1386,91 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Price (100s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/tests/book/fixtures/charts-openpyxl.xlsx
+++ b/tests/book/fixtures/charts-openpyxl.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pie" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scatter" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labels" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -811,6 +815,241 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cost by quarter</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Labels'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Labels'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Labels'!$B$2:$B$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <dLblPos val="outEnd"/>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Visits</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Labels'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="square"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showVal val="1"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Labels'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Labels'!$C$2:$C$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0.0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Share of cost</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Labels'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Labels'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Labels'!$B$2:$B$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showCatName val="1"/>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -950,6 +1189,77 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1473,4 +1783,88 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Visits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C4" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>